--- a/artfynd/A 10336-2022 artfynd.xlsx
+++ b/artfynd/A 10336-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10336-2022 artfynd.xlsx
+++ b/artfynd/A 10336-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110274421</v>
+        <v>113218997</v>
       </c>
       <c r="B2" t="n">
-        <v>102557</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222002</v>
+        <v>3624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häggenås, Jmt</t>
+          <t>Majorsbodarna öster, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492591</v>
       </c>
       <c r="R2" t="n">
-        <v>7024654</v>
+        <v>7024592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +736,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +756,597 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113219003</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87412</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Majorsbodarna öster, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>492629</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7024756</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113218992</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Majorsbodarna öster, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492593</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7024598</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113219008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Majorsbodarna öster, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>492614</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7024717</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110274421</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Häggenås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492564</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Maria Noro-Larsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113219043</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Majorsbodarna öster, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492611</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7024776</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113219044</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Majorsbodarna öster, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492588</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7024584</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10336-2022 artfynd.xlsx
+++ b/artfynd/A 10336-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -765,6 +770,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -858,6 +868,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -955,6 +970,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1052,6 +1072,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1153,6 +1178,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110274421</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1250,6 +1280,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219043</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1347,8 +1382,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219044</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>